--- a/excel-files/NAVOTAS/TANZA ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/NAVOTAS/TANZA ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{875399A3-5C3D-46AB-ACAB-AF9C6A819E12}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A24D252E-0F27-4D8F-BF7A-B75A242B8874}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -67,6 +67,9 @@
     <t>Reading and Literacy</t>
   </si>
   <si>
+    <t>RO</t>
+  </si>
+  <si>
     <t>Language</t>
   </si>
   <si>
@@ -77,6 +80,9 @@
   </si>
   <si>
     <t>Math</t>
+  </si>
+  <si>
+    <t>CO</t>
   </si>
   <si>
     <t>Science</t>
@@ -736,6 +742,12 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -747,12 +759,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3508,17 +3514,25 @@
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="1">
+        <v>406</v>
+      </c>
+      <c r="D2" s="1">
+        <v>615</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G2" s="3">
         <f>IF((C2-D2)&lt;0,0,C2-D2)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
-        <v>0</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="29.25" customHeight="1">
@@ -3526,19 +3540,27 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>406</v>
+      </c>
+      <c r="D3" s="1">
+        <v>615</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="5"/>
       <c r="G3" s="3">
         <f>IF((C3-D3)&lt;0,0,C3-D3)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
-        <v>0</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21" customHeight="1">
@@ -3546,19 +3568,27 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="C4" s="1">
+        <v>406</v>
+      </c>
+      <c r="D4" s="1">
+        <v>615</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G4" s="3">
         <f>IF((C4-D4)&lt;0,0,C4-D4)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
-        <v>0</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25.5" customHeight="1">
@@ -3566,19 +3596,27 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="C5" s="1">
+        <v>406</v>
+      </c>
+      <c r="D5" s="1">
+        <v>615</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G5" s="3">
         <f t="shared" ref="G5:G6" si="0">IF((C5-D5)&lt;0,0,C5-D5)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
-        <v>0</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.149999999999999">
@@ -3586,7 +3624,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -3631,7 +3669,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -3651,7 +3689,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -3671,19 +3709,25 @@
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="D11" s="1">
+        <v>546</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>546</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.149999999999999">
@@ -3691,7 +3735,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -3736,7 +3780,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -3756,7 +3800,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -3776,7 +3820,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3796,7 +3840,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -3816,7 +3860,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -3846,7 +3890,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -3866,39 +3910,55 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="5"/>
+        <v>17</v>
+      </c>
+      <c r="C22" s="1">
+        <v>472</v>
+      </c>
+      <c r="D22" s="1">
+        <v>666</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="19.149999999999999">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="19.5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="5"/>
+        <v>13</v>
+      </c>
+      <c r="C23" s="1">
+        <v>472</v>
+      </c>
+      <c r="D23" s="1">
+        <v>701</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="27" customHeight="1">
@@ -3906,19 +3966,27 @@
         <v>4</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="C24" s="1">
+        <v>472</v>
+      </c>
+      <c r="D24" s="1">
+        <v>701</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="33.75" customHeight="1">
@@ -3926,19 +3994,27 @@
         <v>4</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="C25" s="1">
+        <v>472</v>
+      </c>
+      <c r="D25" s="1">
+        <v>661</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="33.75" customHeight="1">
@@ -3946,19 +4022,27 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="C26" s="1">
+        <v>472</v>
+      </c>
+      <c r="D26" s="1">
+        <v>665</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="33.75" customHeight="1">
@@ -3966,19 +4050,27 @@
         <v>4</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="C27" s="1">
+        <v>472</v>
+      </c>
+      <c r="D27" s="1">
+        <v>701</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="27.75" customHeight="1">
@@ -3986,7 +4078,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -4006,19 +4098,27 @@
         <v>4</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="C29" s="1">
+        <v>472</v>
+      </c>
+      <c r="D29" s="1">
+        <v>701</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4036,19 +4136,27 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="1">
+        <v>473</v>
+      </c>
+      <c r="D31" s="1">
+        <v>570</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4056,7 +4164,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -4076,7 +4184,7 @@
         <v>5</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -4096,7 +4204,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -4116,19 +4224,27 @@
         <v>5</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="C35" s="1">
+        <v>473</v>
+      </c>
+      <c r="D35" s="1">
+        <v>587</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="27.75" customHeight="1">
@@ -4136,19 +4252,27 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="C36" s="1">
+        <v>473</v>
+      </c>
+      <c r="D36" s="1">
+        <v>570</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4156,19 +4280,27 @@
         <v>5</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="C37" s="1">
+        <v>473</v>
+      </c>
+      <c r="D37" s="1">
+        <v>570</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27.75" customHeight="1">
@@ -4176,19 +4308,27 @@
         <v>5</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="C38" s="1">
+        <v>473</v>
+      </c>
+      <c r="D38" s="1">
+        <v>570</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4196,7 +4336,7 @@
         <v>5</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -4226,7 +4366,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -4246,7 +4386,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -4266,7 +4406,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -4286,7 +4426,7 @@
         <v>6</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -4306,7 +4446,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -4326,7 +4466,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -4346,7 +4486,7 @@
         <v>6</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -4366,7 +4506,7 @@
         <v>6</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -4386,7 +4526,7 @@
         <v>6</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -4416,7 +4556,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -4436,7 +4576,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
@@ -4456,7 +4596,7 @@
         <v>7</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
@@ -4476,7 +4616,7 @@
         <v>7</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
@@ -4496,7 +4636,7 @@
         <v>7</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
@@ -4516,7 +4656,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
@@ -4536,7 +4676,7 @@
         <v>7</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
@@ -4556,7 +4696,7 @@
         <v>7</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
@@ -4576,7 +4716,7 @@
         <v>7</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
@@ -4606,7 +4746,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -4626,7 +4766,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -4646,7 +4786,7 @@
         <v>8</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
@@ -4666,7 +4806,7 @@
         <v>8</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="10"/>
@@ -4686,7 +4826,7 @@
         <v>8</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
@@ -4706,7 +4846,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
@@ -4726,7 +4866,7 @@
         <v>8</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
@@ -4746,7 +4886,7 @@
         <v>8</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
@@ -4766,7 +4906,7 @@
         <v>8</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
@@ -4796,7 +4936,7 @@
         <v>9</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
@@ -4816,7 +4956,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
@@ -4836,7 +4976,7 @@
         <v>9</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
@@ -4856,7 +4996,7 @@
         <v>9</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
@@ -4876,7 +5016,7 @@
         <v>9</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
@@ -4896,7 +5036,7 @@
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -4916,7 +5056,7 @@
         <v>9</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
@@ -4936,7 +5076,7 @@
         <v>9</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
@@ -4956,7 +5096,7 @@
         <v>9</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
@@ -4986,7 +5126,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
@@ -5006,7 +5146,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -5026,7 +5166,7 @@
         <v>10</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
@@ -5046,7 +5186,7 @@
         <v>10</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
@@ -5066,7 +5206,7 @@
         <v>10</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
@@ -5086,7 +5226,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -5106,7 +5246,7 @@
         <v>10</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
@@ -5126,7 +5266,7 @@
         <v>10</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
@@ -5146,7 +5286,7 @@
         <v>10</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
@@ -5173,10 +5313,10 @@
     </row>
     <row r="91" spans="1:8" ht="39.75" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -5193,10 +5333,10 @@
     </row>
     <row r="92" spans="1:8" ht="27.75" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
@@ -5213,10 +5353,10 @@
     </row>
     <row r="93" spans="1:8" ht="27.75" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
@@ -5233,10 +5373,10 @@
     </row>
     <row r="94" spans="1:8" ht="27.75" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
@@ -5253,10 +5393,10 @@
     </row>
     <row r="95" spans="1:8" ht="40.5" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
@@ -5273,10 +5413,10 @@
     </row>
     <row r="96" spans="1:8" ht="38.25" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
@@ -5293,10 +5433,10 @@
     </row>
     <row r="97" spans="1:8" ht="27.75" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
@@ -5313,10 +5453,10 @@
     </row>
     <row r="98" spans="1:8" ht="47.25" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
@@ -5338,10 +5478,10 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E21:E29 E2:E6 E14:E19 E8:E12 E31:E39" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F91:F98 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5354,7 +5494,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5384,38 +5524,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5428,81 +5568,81 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="M2" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="N2" s="44" t="s">
         <v>46</v>
       </c>
+      <c r="M2" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="40" t="s">
+        <v>48</v>
+      </c>
       <c r="O2" s="22" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y2" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z2" s="45" t="s">
         <v>58</v>
       </c>
+      <c r="Y2" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z2" s="41" t="s">
+        <v>60</v>
+      </c>
       <c r="AA2" s="26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="32"/>
@@ -5653,7 +5793,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="5">
@@ -5722,7 +5862,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="5">
@@ -5791,7 +5931,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -5860,7 +6000,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -5929,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -5998,7 +6138,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5">
@@ -6067,7 +6207,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="5">
@@ -6144,7 +6284,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6218,7 +6358,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="5">
@@ -6287,7 +6427,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="5">
@@ -6356,7 +6496,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -6425,7 +6565,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -6494,7 +6634,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="5">
@@ -6563,7 +6703,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="5">
@@ -6632,7 +6772,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="5">
@@ -6710,7 +6850,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="38.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6784,7 +6924,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -6853,7 +6993,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="5">
@@ -6922,7 +7062,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="5">
@@ -6991,7 +7131,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -7060,7 +7200,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -7129,7 +7269,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -7198,7 +7338,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="5">
@@ -7267,7 +7407,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -7350,7 +7490,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -7419,7 +7559,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -7488,7 +7628,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="5">
@@ -7557,7 +7697,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -7626,7 +7766,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="5">
@@ -7695,7 +7835,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -7764,7 +7904,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="5">
@@ -7833,7 +7973,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="5">
@@ -7902,7 +8042,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -7985,7 +8125,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -8054,7 +8194,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -8123,7 +8263,7 @@
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="5">
@@ -8192,7 +8332,7 @@
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="5">
@@ -8261,7 +8401,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="5">
@@ -8330,7 +8470,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -8399,7 +8539,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="5">
@@ -8468,7 +8608,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -8537,7 +8677,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="5">
@@ -8620,7 +8760,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -8689,7 +8829,7 @@
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="5">
@@ -8758,7 +8898,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="5">
@@ -8827,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="5">
@@ -8896,7 +9036,7 @@
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="5">
@@ -8965,7 +9105,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -9034,7 +9174,7 @@
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="5">
@@ -9103,7 +9243,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="5">
@@ -9172,7 +9312,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="5">
@@ -9255,7 +9395,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="12">
@@ -9324,7 +9464,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="12">
@@ -9393,7 +9533,7 @@
         <v>7</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="12">
@@ -9462,7 +9602,7 @@
         <v>7</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="12">
@@ -9531,7 +9671,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -9600,7 +9740,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -9669,7 +9809,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="12">
@@ -9738,7 +9878,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -9807,7 +9947,7 @@
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="12">
@@ -9890,7 +10030,7 @@
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="12">
@@ -9959,7 +10099,7 @@
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -10028,7 +10168,7 @@
         <v>8</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="12">
@@ -10097,7 +10237,7 @@
         <v>8</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="12">
@@ -10166,7 +10306,7 @@
         <v>8</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -10235,7 +10375,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="12">
@@ -10304,7 +10444,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -10373,7 +10513,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -10442,7 +10582,7 @@
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="12">
@@ -10525,7 +10665,7 @@
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -10594,7 +10734,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -10663,7 +10803,7 @@
         <v>9</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="12">
@@ -10732,7 +10872,7 @@
         <v>9</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -10801,7 +10941,7 @@
         <v>9</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -10870,7 +11010,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="12">
@@ -10939,7 +11079,7 @@
         <v>9</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -11008,7 +11148,7 @@
         <v>9</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C90" s="10"/>
       <c r="D90" s="12">
@@ -11077,7 +11217,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -11160,7 +11300,7 @@
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -11229,7 +11369,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -11298,7 +11438,7 @@
         <v>10</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="12">
@@ -11367,7 +11507,7 @@
         <v>10</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -11436,7 +11576,7 @@
         <v>10</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -11505,7 +11645,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -11574,7 +11714,7 @@
         <v>10</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -11643,7 +11783,7 @@
         <v>10</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -11712,7 +11852,7 @@
         <v>10</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -11792,10 +11932,10 @@
     </row>
     <row r="103" spans="1:27" ht="38.450000000000003">
       <c r="A103" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="5">
@@ -11861,10 +12001,10 @@
     </row>
     <row r="104" spans="1:27" ht="19.149999999999999">
       <c r="A104" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="5">
@@ -11930,10 +12070,10 @@
     </row>
     <row r="105" spans="1:27" ht="19.149999999999999">
       <c r="A105" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="5">
@@ -11999,10 +12139,10 @@
     </row>
     <row r="106" spans="1:27" ht="19.149999999999999">
       <c r="A106" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="5">
@@ -12068,10 +12208,10 @@
     </row>
     <row r="107" spans="1:27" ht="38.450000000000003">
       <c r="A107" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="5">
@@ -12137,10 +12277,10 @@
     </row>
     <row r="108" spans="1:27" ht="19.149999999999999">
       <c r="A108" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="5">
@@ -12206,10 +12346,10 @@
     </row>
     <row r="109" spans="1:27" ht="38.450000000000003">
       <c r="A109" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="5">
@@ -12275,10 +12415,10 @@
     </row>
     <row r="110" spans="1:27" ht="38.450000000000003">
       <c r="A110" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="5">
@@ -13340,186 +13480,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13539,8 +13499,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13558,7 +13518,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13588,38 +13548,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13632,76 +13592,76 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="M2" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2" s="44" t="s">
         <v>72</v>
       </c>
+      <c r="M2" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" s="40" t="s">
+        <v>74</v>
+      </c>
       <c r="O2" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y2" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z2" s="45" t="s">
         <v>84</v>
       </c>
+      <c r="Y2" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z2" s="41" t="s">
+        <v>86</v>
+      </c>
       <c r="AA2" s="26" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="29.25" customHeight="1">
@@ -13780,7 +13740,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1">
         <v>395</v>
@@ -13851,7 +13811,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>395</v>
@@ -13922,7 +13882,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1">
         <v>395</v>
@@ -13993,7 +13953,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="5">
@@ -14062,7 +14022,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -14131,7 +14091,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -14200,7 +14160,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -14339,7 +14299,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="5">
@@ -14408,7 +14368,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="5">
@@ -14477,7 +14437,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="5">
@@ -14546,7 +14506,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="5">
@@ -14615,7 +14575,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -14684,7 +14644,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -14753,7 +14713,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="5">
@@ -14892,7 +14852,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="5">
@@ -14961,7 +14921,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="5">
@@ -15030,7 +14990,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -15099,7 +15059,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="5">
@@ -15168,7 +15128,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="5">
@@ -15237,7 +15197,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -15306,7 +15266,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -15375,7 +15335,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -15445,7 +15405,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -15514,7 +15474,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="5">
@@ -15583,7 +15543,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -15652,7 +15612,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -15721,7 +15681,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="5">
@@ -15790,7 +15750,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -15859,7 +15819,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
@@ -15928,7 +15888,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -15997,7 +15957,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="5">
@@ -16066,7 +16026,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
@@ -16135,7 +16095,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -16205,7 +16165,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -16274,7 +16234,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -16343,7 +16303,7 @@
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="5">
@@ -16412,7 +16372,7 @@
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="5">
@@ -16481,7 +16441,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="5">
@@ -16550,7 +16510,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -16619,7 +16579,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5">
@@ -16688,7 +16648,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -16757,7 +16717,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="5">
@@ -16826,7 +16786,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5">
@@ -16895,7 +16855,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -16965,7 +16925,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="5">
@@ -17034,7 +16994,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="5">
@@ -17103,7 +17063,7 @@
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="5">
@@ -17172,7 +17132,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -17241,7 +17201,7 @@
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="5">
@@ -17310,7 +17270,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="5">
@@ -17379,7 +17339,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5">
@@ -17448,7 +17408,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="5">
@@ -17517,7 +17477,7 @@
         <v>6</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="5">
@@ -17586,7 +17546,7 @@
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5">
@@ -17655,7 +17615,7 @@
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="5">
@@ -17725,7 +17685,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -17794,7 +17754,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -17863,7 +17823,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="12">
@@ -17932,7 +17892,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -18001,7 +17961,7 @@
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="12">
@@ -18070,7 +18030,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -18139,7 +18099,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12">
@@ -18208,7 +18168,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -18277,7 +18237,7 @@
         <v>7</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="12">
@@ -18346,7 +18306,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12">
@@ -18415,7 +18375,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -18485,7 +18445,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -18554,7 +18514,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -18623,7 +18583,7 @@
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="12">
@@ -18692,7 +18652,7 @@
         <v>8</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="12">
@@ -18761,7 +18721,7 @@
         <v>8</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -18830,7 +18790,7 @@
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -18899,7 +18859,7 @@
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
@@ -18968,7 +18928,7 @@
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -19037,7 +18997,7 @@
         <v>8</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -19106,7 +19066,7 @@
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12">
@@ -19175,7 +19135,7 @@
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -19245,7 +19205,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -19314,7 +19274,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -19383,7 +19343,7 @@
         <v>9</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -19452,7 +19412,7 @@
         <v>9</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -19521,7 +19481,7 @@
         <v>9</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="12">
@@ -19590,7 +19550,7 @@
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -19659,7 +19619,7 @@
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -19728,7 +19688,7 @@
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -19797,7 +19757,7 @@
         <v>9</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -19866,7 +19826,7 @@
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -19935,7 +19895,7 @@
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -20005,7 +19965,7 @@
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="12">
@@ -20074,7 +20034,7 @@
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -20143,7 +20103,7 @@
         <v>10</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="12">
@@ -20212,7 +20172,7 @@
         <v>10</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="12">
@@ -20281,7 +20241,7 @@
         <v>10</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="12">
@@ -20350,7 +20310,7 @@
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="12">
@@ -20419,7 +20379,7 @@
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -20488,7 +20448,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="12">
@@ -20557,7 +20517,7 @@
         <v>10</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="12">
@@ -20626,7 +20586,7 @@
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -20695,7 +20655,7 @@
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
@@ -20762,10 +20722,10 @@
     <row r="114" spans="1:28" s="7" customFormat="1"/>
     <row r="115" spans="1:28" ht="38.450000000000003">
       <c r="A115" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="5">
@@ -20831,10 +20791,10 @@
     </row>
     <row r="116" spans="1:28" ht="19.149999999999999">
       <c r="A116" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="5">
@@ -20900,10 +20860,10 @@
     </row>
     <row r="117" spans="1:28" ht="19.149999999999999">
       <c r="A117" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="5">
@@ -20969,10 +20929,10 @@
     </row>
     <row r="118" spans="1:28" ht="19.149999999999999">
       <c r="A118" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="5">
@@ -21038,10 +20998,10 @@
     </row>
     <row r="119" spans="1:28" ht="38.450000000000003">
       <c r="A119" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="5">
@@ -21107,10 +21067,10 @@
     </row>
     <row r="120" spans="1:28" ht="19.149999999999999">
       <c r="A120" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="5">
@@ -21176,10 +21136,10 @@
     </row>
     <row r="121" spans="1:28" ht="38.450000000000003">
       <c r="A121" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="5">
@@ -21245,10 +21205,10 @@
     </row>
     <row r="122" spans="1:28" ht="38.450000000000003">
       <c r="A122" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="5">
@@ -21823,186 +21783,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22020,8 +21800,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
